--- a/03_Outputs/Transición_ref_dept/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Transición_ref_dept/04_Cluster/Summary_Stats.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2">
-        <v>-0.02541284480635575</v>
+        <v>-0.03208403986812233</v>
       </c>
       <c r="E2">
-        <v>0.7416363758450952</v>
+        <v>0.7390630705647351</v>
       </c>
       <c r="F2">
         <v>-4.197196578932235</v>
       </c>
       <c r="G2">
-        <v>0.570076350306586</v>
+        <v>0.5700763503065862</v>
       </c>
     </row>
     <row r="3">
@@ -430,13 +430,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3">
-        <v>-0.150970314305289</v>
+        <v>-0.1355079393586883</v>
       </c>
       <c r="E3">
-        <v>0.9200805316543488</v>
+        <v>0.9240232360861869</v>
       </c>
       <c r="F3">
         <v>-1.79314253114921</v>
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4">
-        <v>0.269871376620998</v>
+        <v>0.2552593850867292</v>
       </c>
       <c r="E4">
-        <v>0.8381098654054981</v>
+        <v>0.8423929983780266</v>
       </c>
       <c r="F4">
-        <v>-2.228762893657452</v>
+        <v>-2.228762893657451</v>
       </c>
       <c r="G4">
-        <v>2.083767997610404</v>
+        <v>2.083767997610401</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5">
-        <v>-0.0443697013122028</v>
+        <v>-0.06419991515589298</v>
       </c>
       <c r="E5">
-        <v>0.7720324249490177</v>
+        <v>0.7864291385924125</v>
       </c>
       <c r="F5">
-        <v>-1.731044281441919</v>
+        <v>-1.731044281441923</v>
       </c>
       <c r="G5">
-        <v>1.791225967544667</v>
+        <v>1.791225967544666</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6">
-        <v>-0.1646119069967028</v>
+        <v>-0.1613821312507685</v>
       </c>
       <c r="E6">
-        <v>0.9980196681866784</v>
+        <v>0.991837006518514</v>
       </c>
       <c r="F6">
-        <v>-3.377657438923357</v>
+        <v>-3.377657438923359</v>
       </c>
       <c r="G6">
-        <v>2.718449139215524</v>
+        <v>2.718449139215523</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7">
-        <v>0.1794023231448204</v>
+        <v>0.1875463492397068</v>
       </c>
       <c r="E7">
-        <v>0.8059148837973622</v>
+        <v>0.8037784523639688</v>
       </c>
       <c r="F7">
-        <v>-2.114571199073274</v>
+        <v>-2.114571199073277</v>
       </c>
       <c r="G7">
-        <v>2.80318936990205</v>
+        <v>2.803189369902059</v>
       </c>
     </row>
     <row r="8">
@@ -565,16 +565,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8">
-        <v>-0.2395196913927221</v>
+        <v>-0.2343104252166283</v>
       </c>
       <c r="E8">
-        <v>0.8155700928761391</v>
+        <v>0.8114752303424081</v>
       </c>
       <c r="F8">
-        <v>-3.47062216708017</v>
+        <v>-3.470622167080168</v>
       </c>
       <c r="G8">
         <v>1.148394580779897</v>
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9">
-        <v>0.03886847887198185</v>
+        <v>0.03694414396868167</v>
       </c>
       <c r="E9">
-        <v>0.3097051177797235</v>
+        <v>0.3081238821640532</v>
       </c>
       <c r="F9">
-        <v>-0.4619713188321413</v>
+        <v>-0.4619713188321412</v>
       </c>
       <c r="G9">
-        <v>1.246927365638853</v>
+        <v>1.246927365638851</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10">
-        <v>0.2157285031627849</v>
+        <v>0.2210309196277548</v>
       </c>
       <c r="E10">
-        <v>0.5635722478368654</v>
+        <v>0.5617823902109498</v>
       </c>
       <c r="F10">
         <v>-1.682516238251326</v>
       </c>
       <c r="G10">
-        <v>1.019113780145382</v>
+        <v>1.019113780145381</v>
       </c>
     </row>
     <row r="11">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C11">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11">
-        <v>-0.2102504138680607</v>
+        <v>-0.2089071437183284</v>
       </c>
       <c r="E11">
-        <v>0.8601756412951367</v>
+        <v>0.8545791457412838</v>
       </c>
       <c r="F11">
-        <v>-2.328705453757659</v>
+        <v>-2.328705453757658</v>
       </c>
       <c r="G11">
         <v>1.412281000629539</v>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12">
-        <v>-0.03758971238310049</v>
+        <v>-0.01694475781575205</v>
       </c>
       <c r="E12">
-        <v>0.6857394463373719</v>
+        <v>0.7048898693393776</v>
       </c>
       <c r="F12">
         <v>-1.787167423245591</v>
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13">
-        <v>-0.2902642811670298</v>
+        <v>-0.2762831987848396</v>
       </c>
       <c r="E13">
-        <v>0.805347205927741</v>
+        <v>0.8093833218330934</v>
       </c>
       <c r="F13">
-        <v>-2.529225657869897</v>
+        <v>-2.529225657869898</v>
       </c>
       <c r="G13">
         <v>1.946090350098475</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14">
-        <v>0.2613288132215561</v>
+        <v>0.2524602148250217</v>
       </c>
       <c r="E14">
-        <v>1.13076961202182</v>
+        <v>1.125998185143669</v>
       </c>
       <c r="F14">
-        <v>-1.852270485811725</v>
+        <v>-1.852270485811728</v>
       </c>
       <c r="G14">
-        <v>5.872051834822624</v>
+        <v>5.87205183482262</v>
       </c>
     </row>
     <row r="15">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15">
-        <v>-0.01723888794946727</v>
+        <v>-0.02695374423345996</v>
       </c>
       <c r="E15">
-        <v>1.011573131524234</v>
+        <v>1.008505392434733</v>
       </c>
       <c r="F15">
         <v>-1.639955123726799</v>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16">
-        <v>-0.1395000206513707</v>
+        <v>-0.1215047665405037</v>
       </c>
       <c r="E16">
-        <v>0.7169143339764529</v>
+        <v>0.7294780981833542</v>
       </c>
       <c r="F16">
         <v>-2.17941116675173</v>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>-0.3350512748947734</v>
+        <v>-0.3368367797172616</v>
       </c>
       <c r="E17">
-        <v>0.7488397990647522</v>
+        <v>0.7440618845098932</v>
       </c>
       <c r="F17">
-        <v>-2.456126084318659</v>
+        <v>-2.456126084318663</v>
       </c>
       <c r="G17">
-        <v>3.33171916622347</v>
+        <v>3.331719166223466</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18">
-        <v>0.2997075098597006</v>
+        <v>0.2895505629642864</v>
       </c>
       <c r="E18">
-        <v>0.8171186680766618</v>
+        <v>0.8166034601191881</v>
       </c>
       <c r="F18">
-        <v>-1.859172812582831</v>
+        <v>-1.85917281258283</v>
       </c>
       <c r="G18">
-        <v>2.91251939631592</v>
+        <v>2.912519396315923</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19">
-        <v>-0.05493378269420651</v>
+        <v>-0.05719746017430925</v>
       </c>
       <c r="E19">
-        <v>1.107484689448765</v>
+        <v>1.100353784792657</v>
       </c>
       <c r="F19">
-        <v>-5.091141056562349</v>
+        <v>-5.091141056562351</v>
       </c>
       <c r="G19">
-        <v>1.933099784101851</v>
+        <v>1.933099784101848</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20">
-        <v>-0.03329806243681605</v>
+        <v>-0.02525770446547818</v>
       </c>
       <c r="E20">
-        <v>1.15764302743676</v>
+        <v>1.152163980882571</v>
       </c>
       <c r="F20">
-        <v>-3.53749257433838</v>
+        <v>-3.537492574338383</v>
       </c>
       <c r="G20">
-        <v>2.78196434428297</v>
+        <v>2.781964344282971</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21">
-        <v>-0.01870695663771866</v>
+        <v>-0.01552510704079279</v>
       </c>
       <c r="E21">
-        <v>0.5804675234555946</v>
+        <v>0.5773115727965883</v>
       </c>
       <c r="F21">
-        <v>-1.372218107086506</v>
+        <v>-1.372218107086505</v>
       </c>
       <c r="G21">
-        <v>1.566836875812185</v>
+        <v>1.566836875812184</v>
       </c>
     </row>
     <row r="22">
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22">
-        <v>0.3684849831703968</v>
+        <v>0.3636140810744797</v>
       </c>
       <c r="E22">
-        <v>0.8363493641128346</v>
+        <v>0.8319275504225271</v>
       </c>
       <c r="F22">
-        <v>-1.897982906839414</v>
+        <v>-1.897982906839415</v>
       </c>
       <c r="G22">
         <v>2.176683680679193</v>
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23">
-        <v>0.1808070417585218</v>
+        <v>0.1876282803479037</v>
       </c>
       <c r="E23">
-        <v>1.005892226647938</v>
+        <v>1.001043713961331</v>
       </c>
       <c r="F23">
         <v>-1.917608485593091</v>
       </c>
       <c r="G23">
-        <v>2.861245578118104</v>
+        <v>2.861245578118102</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24">
-        <v>-0.01553156203747695</v>
+        <v>-0.01785552962022812</v>
       </c>
       <c r="E24">
-        <v>0.8943106951525487</v>
+        <v>0.8886416089031646</v>
       </c>
       <c r="F24">
-        <v>-2.647417303943672</v>
+        <v>-2.647417303943821</v>
       </c>
       <c r="G24">
-        <v>2.349186330963127</v>
+        <v>2.349186330963114</v>
       </c>
     </row>
     <row r="25">
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25">
-        <v>0.1535730939705602</v>
+        <v>0.1602504754212001</v>
       </c>
       <c r="E25">
-        <v>0.6180563568215801</v>
+        <v>0.6167662923752303</v>
       </c>
       <c r="F25">
         <v>-1.189242768759509</v>
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26">
-        <v>0.2722381152895171</v>
+        <v>0.24989096174079</v>
       </c>
       <c r="E26">
-        <v>0.9946321242283339</v>
+        <v>1.007337820440257</v>
       </c>
       <c r="F26">
-        <v>-1.434306250761593</v>
+        <v>-1.44849270796249</v>
       </c>
       <c r="G26">
-        <v>2.460948688602503</v>
+        <v>2.460948688602504</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D27">
-        <v>0.3563546703356122</v>
+        <v>0.3588180208444046</v>
       </c>
       <c r="E27">
-        <v>0.261186750733464</v>
+        <v>0.2603615755846478</v>
       </c>
       <c r="F27">
-        <v>-0.5291744805744112</v>
+        <v>-0.5291744805744101</v>
       </c>
       <c r="G27">
-        <v>0.5724029658953579</v>
+        <v>0.5724029658953583</v>
       </c>
     </row>
     <row r="28">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C28">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28">
-        <v>-0.1390777677990307</v>
+        <v>-0.1222307273911359</v>
       </c>
       <c r="E28">
-        <v>0.4838933168958394</v>
+        <v>0.5029176257917259</v>
       </c>
       <c r="F28">
         <v>-2.194732178768372</v>
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="C29">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29">
-        <v>0.03884250672082656</v>
+        <v>0.03904170682344694</v>
       </c>
       <c r="E29">
-        <v>0.9475661355730001</v>
+        <v>0.9413131282227414</v>
       </c>
       <c r="F29">
-        <v>-1.621849984713118</v>
+        <v>-1.621849984713117</v>
       </c>
       <c r="G29">
         <v>3.402298193851278</v>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30">
-        <v>-0.1848839478366154</v>
+        <v>-0.1803262826616956</v>
       </c>
       <c r="E30">
-        <v>1.110246909656801</v>
+        <v>1.103643336022203</v>
       </c>
       <c r="F30">
-        <v>-3.607037124529916</v>
+        <v>-3.607037124529915</v>
       </c>
       <c r="G30">
         <v>1.944858086616821</v>
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31">
-        <v>0.09481612253105171</v>
+        <v>0.09696249060084303</v>
       </c>
       <c r="E31">
-        <v>0.8182407937908628</v>
+        <v>0.8130579808864288</v>
       </c>
       <c r="F31">
         <v>-2.792519564879597</v>
       </c>
       <c r="G31">
-        <v>1.525145077839005</v>
+        <v>1.525145077839008</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32">
-        <v>-0.2487353971330135</v>
+        <v>-0.2409238621106172</v>
       </c>
       <c r="E32">
-        <v>0.8744755175160017</v>
+        <v>0.8714034868940221</v>
       </c>
       <c r="F32">
         <v>-1.590213221935761</v>
       </c>
       <c r="G32">
-        <v>3.056942539512557</v>
+        <v>3.056942539512555</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33">
-        <v>0.3431432083135035</v>
+        <v>0.3481987022667314</v>
       </c>
       <c r="E33">
-        <v>0.7667554400995487</v>
+        <v>0.7763741869383196</v>
       </c>
       <c r="F33">
-        <v>-1.244441987613341</v>
+        <v>-1.195135796032279</v>
       </c>
       <c r="G33">
-        <v>1.770429977299429</v>
+        <v>1.771439386181391</v>
       </c>
     </row>
   </sheetData>
